--- a/data-manipulation-scripts/sheets-cleanup/sheets/VOLANTE MAGNETO.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/VOLANTE MAGNETO.xlsx
@@ -110,10 +110,10 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
+      <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
@@ -413,10 +413,10 @@
       <c r="B3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="4">
-        <v>1.0</v>
+      <c r="C3" s="6">
+        <v>0.0</v>
       </c>
-      <c r="D3" s="6"/>
+      <c r="D3" s="7"/>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
@@ -450,7 +450,7 @@
       <c r="C4" s="4">
         <v>1.0</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="6">
         <v>240.0</v>
       </c>
       <c r="E4" s="5"/>
@@ -486,7 +486,7 @@
       <c r="C5" s="8">
         <v>1.0</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="6">
         <v>460.0</v>
       </c>
       <c r="E5" s="5"/>
